--- a/проект/Калькулятор_стоимости_вариативности.xlsx
+++ b/проект/Калькулятор_стоимости_вариативности.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пары блюд" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Отходы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии отходов" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Два сценария" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +32,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +55,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2EFE6"/>
+        <bgColor rgb="00F2EFE6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,12 +74,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,10 +450,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Позиция</t>
@@ -529,11 +558,11 @@
         <v>110</v>
       </c>
       <c r="H2">
-        <f>ROUND(C2*D2/1000*F2,2)</f>
+        <f>ROUND(D2*F2/1000,2)</f>
         <v/>
       </c>
       <c r="I2">
-        <f>ROUND(C2*E2/1000*G2,2)</f>
+        <f>ROUND(E2*G2/1000,2)</f>
         <v/>
       </c>
       <c r="J2">
@@ -577,11 +606,11 @@
         <v>260</v>
       </c>
       <c r="H3">
-        <f>ROUND(C3*D3/1000*F3,2)</f>
+        <f>ROUND(D3*F3/1000,2)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>ROUND(C3*E3/1000*G3,2)</f>
+        <f>ROUND(E3*G3/1000,2)</f>
         <v/>
       </c>
       <c r="J3">
@@ -625,11 +654,11 @@
         <v>65</v>
       </c>
       <c r="H4">
-        <f>ROUND(C4*D4/1000*F4,2)</f>
+        <f>ROUND(D4*F4/1000,2)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>ROUND(C4*E4/1000*G4,2)</f>
+        <f>ROUND(E4*G4/1000,2)</f>
         <v/>
       </c>
       <c r="J4">
@@ -673,11 +702,11 @@
         <v>55</v>
       </c>
       <c r="H5">
-        <f>ROUND(C5*D5/1000*F5,2)</f>
+        <f>ROUND(D5*F5/1000,2)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>ROUND(C5*E5/1000*G5,2)</f>
+        <f>ROUND(E5*G5/1000,2)</f>
         <v/>
       </c>
       <c r="J5">
@@ -692,11 +721,8 @@
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Итого разница, руб/мес</t>
         </is>
@@ -706,7 +732,17 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Жёлтые ячейки — ввод. Стоимости порций считаются как норма_г × цена_руб/кг / 1000. Цифры — учебная заглушка, не себестоимость конкретного дома.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:L9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -717,8 +753,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -869,7 +911,17 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Маркировка: без своего 7-дневного замера это не экономика дома, а арифметика примера.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -882,6 +934,13 @@
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -982,4 +1041,116 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Что меняется</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Пример входа (заглушка)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Что считает калькулятор</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Чего считать нельзя</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>1. Собственный пищеблок: пара эквивалентов внутри нормы</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Гречка / рис как взаимозаменяемый гарнир; нормы закладки сопоставимы; меняется только доля выбора</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>См. лист «Пары блюд», строка «Каша гарнирная»: учебные 90 и 110 руб/кг</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Разница сырьевой стоимости порции и месяца при заданном числе порций</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Не себестоимость Серафимовского и не доказательство экономии. Подставляйте свои цены и свой замер отходов</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2. Аутсорсинг: две позиции в ТЗ вместо монопозиции</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>В спецификации — группа «крупы гарнирные», не одна крупа; поставщик отчитывается о доле выбора</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Те же учебные цены порции; контрактная цена услуги обычно выше сырьевой в 3–6 раз (раздел 29, I-dcbp) — в калькулятор не подставлять «с потолка»</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Сырьевой слой пары. Полную стоимость аутсорсинга считать только построчно: сырьё, труд, логистика, наценка</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Не обещание «вариативность бесплатна» и не обоснование снижения цены контракта. Пилот без новой сметы ≠ без затрат (посуда, весы, обучение, иногда ставки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Оба сценария — подписанные учебные заглушки для семинара 25–27.08.2026. Жёлтый ввод на листах 1–2 замените своими числами до любого разговора с учредителем.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>